--- a/apps_results_MAK_REINFORCE/RPA_6species_8rxns/RPA_6species_8rxns_MAK_REINFORCE.xlsx
+++ b/apps_results_MAK_REINFORCE/RPA_6species_8rxns/RPA_6species_8rxns_MAK_REINFORCE.xlsx
@@ -10,14 +10,14 @@
     <sheet r:id="rId1" sheetId="1" name="Data"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Data'!$A$1:$W$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Data'!$A$1:$W$4</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="40">
   <si>
     <t>Timestamp</t>
   </si>
@@ -127,7 +127,16 @@
     <t>https://www.comet.com/maurice-filo/rpa-6species-8rxns-mak-reinforce/146edf9f085b40c1bb421a94776e8900</t>
   </si>
   <si>
-    <t>Same conditions as previous run.</t>
+    <t>Same conditions as previous run but decreased the number of epochs to 300. Same results</t>
+  </si>
+  <si>
+    <t>2025-11-24 09:59:17</t>
+  </si>
+  <si>
+    <t>https://www.comet.com/maurice-filo/rpa-6species-8rxns-mak-reinforce/8ad21ba550414dc3891df4dde3b6d7fc</t>
+  </si>
+  <si>
+    <t>Same conditions as previous run. Same as before</t>
   </si>
 </sst>
 </file>
@@ -135,7 +144,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -146,12 +155,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -183,15 +186,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -502,35 +502,35 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:W4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="4" width="20.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="4" width="11.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="4" width="17.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="4" width="6.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="4" width="43.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="4" width="254.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="4" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="5" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="4" width="16.005" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="5" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="5" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="5" width="16.005" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="5" width="7.005" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="4" width="74.005" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="5" width="16.005" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="5" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="5" width="16.005" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="5" width="13.005" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="5" width="21.005" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="5" width="17.005" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="4" width="25.005" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="4" width="131.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="3" width="20.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="3" width="11.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="3" width="17.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="3" width="6.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="3" width="46.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="3" width="254.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="3" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="4" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="3" width="16.005" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="4" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="4" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="4" width="16.005" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="4" width="7.005" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="3" width="74.005" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="4" width="16.005" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="4" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="4" width="16.005" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="4" width="13.005" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="4" width="21.005" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="4" width="17.005" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="3" width="25.005" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="3" width="131.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -601,7 +601,7 @@
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
@@ -672,16 +672,22 @@
         <v>33</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="F3" s="1" t="s">
         <v>36</v>
       </c>
@@ -691,49 +697,120 @@
       <c r="H3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="2">
         <v>300</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="2">
         <v>5</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="2">
         <v>1024</v>
       </c>
-      <c r="M3" s="3">
+      <c r="M3" s="2">
         <v>10240</v>
       </c>
-      <c r="N3" s="3">
+      <c r="N3" s="2">
         <v>128</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="P3" s="3">
+      <c r="P3" s="2">
         <v>10</v>
       </c>
-      <c r="Q3" s="3">
+      <c r="Q3" s="2">
         <v>30</v>
       </c>
-      <c r="R3" s="3">
+      <c r="R3" s="2">
         <v>100</v>
       </c>
-      <c r="S3" s="3">
+      <c r="S3" s="2">
         <v>1000</v>
       </c>
-      <c r="T3" s="3">
+      <c r="T3" s="2">
         <v>1</v>
       </c>
-      <c r="U3" s="3">
+      <c r="U3" s="2">
         <v>27</v>
       </c>
       <c r="V3" s="1" t="s">
         <v>32</v>
       </c>
       <c r="W3" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+      <c r="A4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="2">
+        <v>300</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K4" s="2">
+        <v>5</v>
+      </c>
+      <c r="L4" s="2">
+        <v>1024</v>
+      </c>
+      <c r="M4" s="2">
+        <v>10240</v>
+      </c>
+      <c r="N4" s="2">
+        <v>128</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="P4" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>30</v>
+      </c>
+      <c r="R4" s="2">
+        <v>100</v>
+      </c>
+      <c r="S4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="T4" s="2">
+        <v>1</v>
+      </c>
+      <c r="U4" s="2">
+        <v>27</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="W4" s="1" t="s">
         <v>33</v>
       </c>
     </row>

--- a/apps_results_MAK_REINFORCE/RPA_6species_8rxns/RPA_6species_8rxns_MAK_REINFORCE.xlsx
+++ b/apps_results_MAK_REINFORCE/RPA_6species_8rxns/RPA_6species_8rxns_MAK_REINFORCE.xlsx
@@ -10,14 +10,14 @@
     <sheet r:id="rId1" sheetId="1" name="Data"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Data'!$A$1:$W$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Data'!$A$1:$W$5</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="43">
   <si>
     <t>Timestamp</t>
   </si>
@@ -137,6 +137,15 @@
   </si>
   <si>
     <t>Same conditions as previous run. Same as before</t>
+  </si>
+  <si>
+    <t>2026-01-08 12:18:49</t>
+  </si>
+  <si>
+    <t>https://www.comet.com/maurice-filo/rpa-6species-8rxns-mak-reinforce/f2a0b44b161a4dccaf75b6ca88e92f36</t>
+  </si>
+  <si>
+    <t>run-1.</t>
   </si>
 </sst>
 </file>
@@ -144,7 +153,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -155,6 +164,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -186,12 +201,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -502,35 +520,35 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:W4"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="3" width="20.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="3" width="11.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="3" width="17.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="3" width="6.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="3" width="46.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="3" width="254.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="3" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="4" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="3" width="16.005" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="4" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="4" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="4" width="16.005" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="4" width="7.005" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="3" width="74.005" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="4" width="16.005" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="4" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="4" width="16.005" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="4" width="13.005" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="4" width="21.005" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="4" width="17.005" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="3" width="25.005" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="3" width="131.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="4" width="20.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="4" width="11.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="4" width="17.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="4" width="6.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="4" width="88.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="4" width="254.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="4" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="5" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="4" width="16.005" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="5" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="5" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="5" width="16.005" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="5" width="7.005" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="4" width="74.005" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="5" width="16.005" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="5" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="5" width="16.005" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="5" width="13.005" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="5" width="21.005" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="5" width="17.005" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="4" width="25.005" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="4" width="131.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -601,7 +619,7 @@
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
@@ -672,7 +690,7 @@
         <v>33</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
@@ -743,7 +761,7 @@
         <v>33</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="1" t="s">
         <v>37</v>
       </c>
@@ -811,6 +829,71 @@
         <v>32</v>
       </c>
       <c r="W4" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18">
+      <c r="A5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="3">
+        <v>300</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" s="3">
+        <v>5</v>
+      </c>
+      <c r="L5" s="3">
+        <v>1024</v>
+      </c>
+      <c r="M5" s="3">
+        <v>10240</v>
+      </c>
+      <c r="N5" s="3">
+        <v>128</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="P5" s="3">
+        <v>10</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>30</v>
+      </c>
+      <c r="R5" s="3">
+        <v>100</v>
+      </c>
+      <c r="S5" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T5" s="3">
+        <v>1</v>
+      </c>
+      <c r="U5" s="3">
+        <v>27</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="W5" s="1" t="s">
         <v>33</v>
       </c>
     </row>

--- a/apps_results_MAK_REINFORCE/RPA_6species_8rxns/RPA_6species_8rxns_MAK_REINFORCE.xlsx
+++ b/apps_results_MAK_REINFORCE/RPA_6species_8rxns/RPA_6species_8rxns_MAK_REINFORCE.xlsx
@@ -10,14 +10,14 @@
     <sheet r:id="rId1" sheetId="1" name="Data"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Data'!$A$1:$W$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">=Data!$A$1:$W$4</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="40">
   <si>
     <t>Timestamp</t>
   </si>
@@ -88,10 +88,10 @@
     <t>Structure Head Temperature</t>
   </si>
   <si>
-    <t>2025-11-23 16:00:40</t>
-  </si>
-  <si>
-    <t>https://www.comet.com/maurice-filo/rpa-6species-8rxns-mak-reinforce/9a5cee7e94e54f8b90543c8924f49894</t>
+    <t>2026-01-10 10:29:01</t>
+  </si>
+  <si>
+    <t>https://www.comet.com/maurice-filo/rpa-6species-8rxns-mak-reinforce/3830d7922aea4b718e53cb23dc367f0e</t>
   </si>
   <si>
     <t>Yes*</t>
@@ -100,7 +100,7 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>Good convergence and topological diversity</t>
+    <t xml:space="preserve">run-1. Removed actuation reaction from the template. Added SIL. </t>
   </si>
   <si>
     <t>{'entropy_weight': 0.001, 'entropy_weight_structure_head': 1.0, 'entropy_weight_continuous_head': 0.5, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
@@ -118,34 +118,25 @@
     <t>{'type': 'lognormal_1D'}</t>
   </si>
   <si>
-    <t>{'target_entropy_ratio_to_max': np.float64(0.24277413243264), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
-  </si>
-  <si>
-    <t>2025-11-24 07:23:22</t>
-  </si>
-  <si>
-    <t>https://www.comet.com/maurice-filo/rpa-6species-8rxns-mak-reinforce/146edf9f085b40c1bb421a94776e8900</t>
-  </si>
-  <si>
-    <t>Same conditions as previous run but decreased the number of epochs to 300. Same results</t>
-  </si>
-  <si>
-    <t>2025-11-24 09:59:17</t>
-  </si>
-  <si>
-    <t>https://www.comet.com/maurice-filo/rpa-6species-8rxns-mak-reinforce/8ad21ba550414dc3891df4dde3b6d7fc</t>
-  </si>
-  <si>
-    <t>Same conditions as previous run. Same as before</t>
-  </si>
-  <si>
-    <t>2026-01-08 12:18:49</t>
-  </si>
-  <si>
-    <t>https://www.comet.com/maurice-filo/rpa-6species-8rxns-mak-reinforce/f2a0b44b161a4dccaf75b6ca88e92f36</t>
-  </si>
-  <si>
-    <t>run-1.</t>
+    <t>{'target_entropy_ratio_to_max': np.float64(0.25751108605227985), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+  </si>
+  <si>
+    <t>2026-01-10 17:25:49</t>
+  </si>
+  <si>
+    <t>https://www.comet.com/maurice-filo/rpa-6species-8rxns-mak-reinforce/be184296efce440c9cf18f0269c2afe2</t>
+  </si>
+  <si>
+    <t>run-2. Same conditions as before.</t>
+  </si>
+  <si>
+    <t>2026-01-11 15:47:49</t>
+  </si>
+  <si>
+    <t>https://www.comet.com/maurice-filo/rpa-6species-8rxns-mak-reinforce/08ffd211df1c4b81b1008acbed717b2b</t>
+  </si>
+  <si>
+    <t>run-3. Same conditions as before.</t>
   </si>
 </sst>
 </file>
@@ -153,7 +144,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -164,12 +155,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -201,15 +186,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -520,32 +502,32 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:W4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="4" width="20.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="4" width="11.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="4" width="17.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="4" width="6.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="4" width="88.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="4" width="254.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="4" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="5" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="4" width="16.005" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="5" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="5" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="5" width="16.005" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="5" width="7.005" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="4" width="74.005" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="5" width="16.005" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="5" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="5" width="16.005" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="5" width="13.005" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="5" width="21.005" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="5" width="17.005" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="4" width="25.005" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="4" width="131.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="3" width="20.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="3" width="11.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="3" width="17.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="3" width="6.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="3" width="88.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="3" width="254.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="3" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="4" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="3" width="16.005" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="4" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="4" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="4" width="16.005" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="4" width="7.005" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="3" width="74.005" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="4" width="16.005" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="4" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="4" width="16.005" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="4" width="13.005" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="4" width="21.005" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="4" width="17.005" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="3" width="25.005" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="3" width="134.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -645,7 +627,7 @@
         <v>29</v>
       </c>
       <c r="I2" s="2">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>30</v>
@@ -829,71 +811,6 @@
         <v>32</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18">
-      <c r="A5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="3">
-        <v>300</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K5" s="3">
-        <v>5</v>
-      </c>
-      <c r="L5" s="3">
-        <v>1024</v>
-      </c>
-      <c r="M5" s="3">
-        <v>10240</v>
-      </c>
-      <c r="N5" s="3">
-        <v>128</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="P5" s="3">
-        <v>10</v>
-      </c>
-      <c r="Q5" s="3">
-        <v>30</v>
-      </c>
-      <c r="R5" s="3">
-        <v>100</v>
-      </c>
-      <c r="S5" s="3">
-        <v>1000</v>
-      </c>
-      <c r="T5" s="3">
-        <v>1</v>
-      </c>
-      <c r="U5" s="3">
-        <v>27</v>
-      </c>
-      <c r="V5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="W5" s="1" t="s">
         <v>33</v>
       </c>
     </row>
